--- a/Compititor's_Price/IKO_Prices/IKO_Prices_23-07-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_23-07-2025.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/30mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-16.html</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/60mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-8.html</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/70mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-7.html</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/110mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-4.html</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/150mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-2.html</t>
         </is>
       </c>
     </row>
